--- a/Employee_Reports_wi52/Rizardo Villalobos Q0048.xlsx
+++ b/Employee_Reports_wi52/Rizardo Villalobos Q0048.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -606,11 +606,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-379</v>
+        <v>-387</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -670,41 +670,41 @@
       <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>18-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>18-Aug-2026</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -729,11 +729,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
